--- a/templates/Template-2-DFMEA-New.xlsx
+++ b/templates/Template-2-DFMEA-New.xlsx
@@ -6,9 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20750" windowHeight="10480" tabRatio="795" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DFMEA标准表格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PFMEA标准表格" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="措施优先级准则" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DFMEA Standard Form" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PFMEA Standard Form" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Priority Criteria" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
@@ -4303,7 +4303,7 @@
     <definedName name="vvvvv" localSheetId="0">vvvvv</definedName>
     <definedName name="xcgg" localSheetId="0">xcgg</definedName>
     <definedName name="zhang" localSheetId="0">zhang</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DFMEA标准表格'!$D$1:$AO$72</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DFMEA Standard Form'!$D$1:$AO$72</definedName>
     <definedName name="__GoA1" localSheetId="1">__GoA1</definedName>
     <definedName name="_GoA1" localSheetId="1">_GoA1</definedName>
     <definedName name="ADL" localSheetId="1">ADL</definedName>
@@ -4350,7 +4350,7 @@
     <definedName name="vvvvv" localSheetId="1">vvvvv</definedName>
     <definedName name="xcgg" localSheetId="1">xcgg</definedName>
     <definedName name="zhang" localSheetId="1">zhang</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'PFMEA标准表格'!$D$1:$AS$72</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'PFMEA Standard Form'!$D$1:$AS$72</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -8353,7 +8353,7 @@
     <row r="3" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Company Name:</t>
+          <t>Company name:</t>
         </is>
       </c>
       <c r="E3" s="33" t="n"/>
@@ -8361,7 +8361,7 @@
       <c r="G3" s="96" t="n"/>
       <c r="H3" s="32" t="inlineStr">
         <is>
-          <t>项目名称：</t>
+          <t>Project name:</t>
         </is>
       </c>
       <c r="I3" s="33" t="n"/>
@@ -8373,7 +8373,7 @@
       <c r="O3" s="96" t="n"/>
       <c r="P3" s="32" t="inlineStr">
         <is>
-          <t>DFMEA ID编号：</t>
+          <t>DFMEA ID:</t>
         </is>
       </c>
       <c r="Q3" s="33" t="n"/>
@@ -8394,7 +8394,7 @@
     <row r="4" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Plant Address:</t>
+          <t>Plant address:</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -8402,7 +8402,7 @@
       <c r="G4" s="96" t="n"/>
       <c r="H4" s="32" t="inlineStr">
         <is>
-          <t>DFMEA开始时间：</t>
+          <t>DFMEA start date:</t>
         </is>
       </c>
       <c r="I4" s="52" t="n"/>
@@ -8414,7 +8414,7 @@
       <c r="O4" s="96" t="n"/>
       <c r="P4" s="34" t="inlineStr">
         <is>
-          <t>设计Responsible：</t>
+          <t>Design responsible:</t>
         </is>
       </c>
       <c r="Q4" s="33" t="n"/>
@@ -8435,7 +8435,7 @@
     <row r="5" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Customer Name:</t>
+          <t>Customer name:</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -8443,7 +8443,7 @@
       <c r="G5" s="96" t="n"/>
       <c r="H5" s="32" t="inlineStr">
         <is>
-          <t>DFMEA修订时间：</t>
+          <t>DFMEA revision date:</t>
         </is>
       </c>
       <c r="I5" s="52" t="n"/>
@@ -8455,7 +8455,7 @@
       <c r="O5" s="96" t="n"/>
       <c r="P5" s="32" t="inlineStr">
         <is>
-          <t>保密等级：</t>
+          <t>Confidentiality level:</t>
         </is>
       </c>
       <c r="Q5" s="33" t="n"/>
@@ -8476,7 +8476,7 @@
     <row r="6" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="D6" s="34" t="inlineStr">
         <is>
-          <t>Model Year / Project:</t>
+          <t>Model year / project:</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -8484,7 +8484,7 @@
       <c r="G6" s="96" t="n"/>
       <c r="H6" s="32" t="inlineStr">
         <is>
-          <t>跨职能小组：</t>
+          <t>Cross-functional team:</t>
         </is>
       </c>
       <c r="I6" s="53" t="n"/>
@@ -8571,12 +8571,12 @@
     <row r="9" ht="18" customFormat="1" customHeight="1" s="86">
       <c r="C9" s="38" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Continuous improvement</t>
         </is>
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
-          <t>System Analysis</t>
+          <t>System analysis</t>
         </is>
       </c>
       <c r="E9" s="93" t="n"/>
@@ -8586,7 +8586,7 @@
       <c r="I9" s="94" t="n"/>
       <c r="J9" s="56" t="inlineStr">
         <is>
-          <t>失效分析及降低风险</t>
+          <t>Failure analysis &amp; risk reduction</t>
         </is>
       </c>
       <c r="K9" s="93" t="n"/>
@@ -8628,7 +8628,7 @@
       <c r="I10" s="94" t="n"/>
       <c r="J10" s="40" t="inlineStr">
         <is>
-          <t>步骤4 - Failure analysis （失效分析）</t>
+          <t>Step 4 — Failure Analysis</t>
         </is>
       </c>
       <c r="K10" s="93" t="n"/>
@@ -8636,7 +8636,7 @@
       <c r="M10" s="94" t="n"/>
       <c r="N10" s="57" t="inlineStr">
         <is>
-          <t>步骤5 - Riske analysis （风险分析）</t>
+          <t>Step 5 — Risk Analysis</t>
         </is>
       </c>
       <c r="O10" s="93" t="n"/>
@@ -8645,7 +8645,7 @@
       <c r="R10" s="93" t="n"/>
       <c r="S10" s="40" t="inlineStr">
         <is>
-          <t>步骤6 - Optimization （优化）</t>
+          <t>Step 6 — Optimization</t>
         </is>
       </c>
       <c r="T10" s="93" t="n"/>
@@ -8668,43 +8668,42 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t>History / Change Authorization
-(if applicable)</t>
+          <t>History / change authorization (if applicable)</t>
         </is>
       </c>
       <c r="D11" s="43" t="inlineStr">
         <is>
-          <t>1. Higher Level</t>
+          <t>1. Higher level</t>
         </is>
       </c>
       <c r="E11" s="90" t="inlineStr">
         <is>
-          <t>2. Focus Element</t>
+          <t>2. Focus element</t>
         </is>
       </c>
       <c r="F11" s="91" t="inlineStr">
         <is>
-          <t>3. Next Lower Level or Characteristic Type</t>
+          <t>3. Next lower level or characteristic type</t>
         </is>
       </c>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>1. Higher Level功能及要求</t>
+          <t>1. Higher-level function &amp; requirements</t>
         </is>
       </c>
       <c r="H11" s="90" t="inlineStr">
         <is>
-          <t>关注要素功能及要求</t>
+          <t>Focus element function &amp; requirements</t>
         </is>
       </c>
       <c r="I11" s="91" t="inlineStr">
         <is>
-          <t>下一低层级的功能及要求或特性</t>
+          <t>Next lower-level function/requirement or characteristic</t>
         </is>
       </c>
       <c r="J11" s="43" t="inlineStr">
         <is>
-          <t>1.对于上一高层级要素或最终用户的Failure Effect (FE)</t>
+          <t>1. Failure Effect (FE) on higher-level element and/or end user</t>
         </is>
       </c>
       <c r="K11" s="59" t="inlineStr">
@@ -8714,17 +8713,17 @@
       </c>
       <c r="L11" s="44" t="inlineStr">
         <is>
-          <t>Focus Element Failure Mode (FM)</t>
+          <t>Focus element failure mode (FM)</t>
         </is>
       </c>
       <c r="M11" s="45" t="inlineStr">
         <is>
-          <t>下一低层级要素或特性的Failure Cause (FC)</t>
+          <t>Failure Cause (FC) of next lower-level element/characteristic</t>
         </is>
       </c>
       <c r="N11" s="60" t="inlineStr">
         <is>
-          <t>当前对失效起因的预防控制（PC)</t>
+          <t>Current Prevention Control (PC) for failure cause</t>
         </is>
       </c>
       <c r="O11" s="59" t="inlineStr">
@@ -8734,7 +8733,7 @@
       </c>
       <c r="P11" s="60" t="inlineStr">
         <is>
-          <t>对失效起因或失效模式的当前探测控制（DC)</t>
+          <t>Current Detection Control (DC) for cause or mode</t>
         </is>
       </c>
       <c r="Q11" s="59" t="inlineStr">
@@ -8749,23 +8748,23 @@
       </c>
       <c r="S11" s="60" t="inlineStr">
         <is>
-          <t>Prevention Actions</t>
+          <t>Prevention actions</t>
         </is>
       </c>
       <c r="T11" s="60" t="inlineStr">
         <is>
-          <t>Detection Actions</t>
+          <t>Detection actions</t>
         </is>
       </c>
       <c r="U11" s="80" t="inlineStr">
         <is>
-          <t>Responsible姓名</t>
+          <t>Responsible person</t>
         </is>
       </c>
       <c r="V11" s="80" t="inlineStr">
         <is>
-          <t>目标
-Completion Date</t>
+          <t>Target
+completion date</t>
         </is>
       </c>
       <c r="W11" s="80" t="inlineStr">
@@ -8775,12 +8774,12 @@
       </c>
       <c r="X11" s="80" t="inlineStr">
         <is>
-          <t>措施证据</t>
+          <t>Action evidence</t>
         </is>
       </c>
       <c r="Y11" s="80" t="inlineStr">
         <is>
-          <t>Completion Date</t>
+          <t>Completion date</t>
         </is>
       </c>
       <c r="Z11" s="59" t="inlineStr">
@@ -8822,10 +8821,7 @@
       <c r="O12" s="65" t="n"/>
       <c r="P12" s="64" t="n"/>
       <c r="Q12" s="65" t="n"/>
-      <c r="R12" s="100">
-        <f>IF(OR(K12="",O12="",Q12=""),"-",LOOKUP(1,0/((K12&gt;=--MID([24]AP准则!$A$2:$A$70,1,FIND("-",[24]AP准则!$A$2:$A$70)-1))*(K12&lt;=--MID([24]AP准则!$A$2:$A$70,FIND("-",[24]AP准则!$A$2:$A$70)+1,2))*(O12&gt;=--MID([24]AP准则!$B$2:$B$70,1,FIND("-",[24]AP准则!$B$2:$B$70)-1))*(O12&lt;=--MID([24]AP准则!$B$2:$B$70,FIND("-",[24]AP准则!$B$2:$B$70)+1,2))*(Q12&gt;=--MID([24]AP准则!$C$2:$C$70,1,FIND("-",[24]AP准则!$C$2:$C$70)-1))*(Q12&lt;=--MID([24]AP准则!$C$2:$C$70,FIND("-",[24]AP准则!$C$2:$C$70)+1,2))),[24]AP准则!$D$2:$D$70))</f>
-        <v/>
-      </c>
+      <c r="R12" s="100" t="n"/>
       <c r="S12" s="64" t="n"/>
       <c r="T12" s="64" t="n"/>
       <c r="U12" s="64" t="n"/>
@@ -8859,10 +8855,7 @@
       <c r="O13" s="65" t="n"/>
       <c r="P13" s="65" t="n"/>
       <c r="Q13" s="65" t="n"/>
-      <c r="R13" s="100">
-        <f>IF(OR(K13="",O13="",Q13=""),"-",LOOKUP(1,0/((K13&gt;=--MID([24]AP准则!$A$2:$A$70,1,FIND("-",[24]AP准则!$A$2:$A$70)-1))*(K13&lt;=--MID([24]AP准则!$A$2:$A$70,FIND("-",[24]AP准则!$A$2:$A$70)+1,2))*(O13&gt;=--MID([24]AP准则!$B$2:$B$70,1,FIND("-",[24]AP准则!$B$2:$B$70)-1))*(O13&lt;=--MID([24]AP准则!$B$2:$B$70,FIND("-",[24]AP准则!$B$2:$B$70)+1,2))*(Q13&gt;=--MID([24]AP准则!$C$2:$C$70,1,FIND("-",[24]AP准则!$C$2:$C$70)-1))*(Q13&lt;=--MID([24]AP准则!$C$2:$C$70,FIND("-",[24]AP准则!$C$2:$C$70)+1,2))),[24]AP准则!$D$2:$D$70))</f>
-        <v/>
-      </c>
+      <c r="R13" s="100" t="n"/>
       <c r="S13" s="65" t="n"/>
       <c r="T13" s="65" t="n"/>
       <c r="U13" s="65" t="n"/>
@@ -8893,10 +8886,7 @@
       <c r="O14" s="65" t="n"/>
       <c r="P14" s="67" t="n"/>
       <c r="Q14" s="65" t="n"/>
-      <c r="R14" s="100">
-        <f>IF(OR(K14="",O14="",Q14=""),"-",LOOKUP(1,0/((K14&gt;=--MID([24]AP准则!$A$2:$A$70,1,FIND("-",[24]AP准则!$A$2:$A$70)-1))*(K14&lt;=--MID([24]AP准则!$A$2:$A$70,FIND("-",[24]AP准则!$A$2:$A$70)+1,2))*(O14&gt;=--MID([24]AP准则!$B$2:$B$70,1,FIND("-",[24]AP准则!$B$2:$B$70)-1))*(O14&lt;=--MID([24]AP准则!$B$2:$B$70,FIND("-",[24]AP准则!$B$2:$B$70)+1,2))*(Q14&gt;=--MID([24]AP准则!$C$2:$C$70,1,FIND("-",[24]AP准则!$C$2:$C$70)-1))*(Q14&lt;=--MID([24]AP准则!$C$2:$C$70,FIND("-",[24]AP准则!$C$2:$C$70)+1,2))),[24]AP准则!$D$2:$D$70))</f>
-        <v/>
-      </c>
+      <c r="R14" s="100" t="n"/>
       <c r="S14" s="65" t="n"/>
       <c r="T14" s="65" t="n"/>
       <c r="U14" s="65" t="n"/>
@@ -8927,10 +8917,7 @@
       <c r="O15" s="65" t="n"/>
       <c r="P15" s="65" t="n"/>
       <c r="Q15" s="65" t="n"/>
-      <c r="R15" s="100">
-        <f>IF(OR(K15="",O15="",Q15=""),"-",LOOKUP(1,0/((K15&gt;=--MID([24]AP准则!$A$2:$A$70,1,FIND("-",[24]AP准则!$A$2:$A$70)-1))*(K15&lt;=--MID([24]AP准则!$A$2:$A$70,FIND("-",[24]AP准则!$A$2:$A$70)+1,2))*(O15&gt;=--MID([24]AP准则!$B$2:$B$70,1,FIND("-",[24]AP准则!$B$2:$B$70)-1))*(O15&lt;=--MID([24]AP准则!$B$2:$B$70,FIND("-",[24]AP准则!$B$2:$B$70)+1,2))*(Q15&gt;=--MID([24]AP准则!$C$2:$C$70,1,FIND("-",[24]AP准则!$C$2:$C$70)-1))*(Q15&lt;=--MID([24]AP准则!$C$2:$C$70,FIND("-",[24]AP准则!$C$2:$C$70)+1,2))),[24]AP准则!$D$2:$D$70))</f>
-        <v/>
-      </c>
+      <c r="R15" s="100" t="n"/>
       <c r="S15" s="65" t="n"/>
       <c r="T15" s="65" t="n"/>
       <c r="U15" s="65" t="n"/>
@@ -8961,10 +8948,7 @@
       <c r="O16" s="65" t="n"/>
       <c r="P16" s="67" t="n"/>
       <c r="Q16" s="65" t="n"/>
-      <c r="R16" s="100">
-        <f>IF(OR(K16="",O16="",Q16=""),"-",LOOKUP(1,0/((K16&gt;=--MID([24]AP准则!$A$2:$A$70,1,FIND("-",[24]AP准则!$A$2:$A$70)-1))*(K16&lt;=--MID([24]AP准则!$A$2:$A$70,FIND("-",[24]AP准则!$A$2:$A$70)+1,2))*(O16&gt;=--MID([24]AP准则!$B$2:$B$70,1,FIND("-",[24]AP准则!$B$2:$B$70)-1))*(O16&lt;=--MID([24]AP准则!$B$2:$B$70,FIND("-",[24]AP准则!$B$2:$B$70)+1,2))*(Q16&gt;=--MID([24]AP准则!$C$2:$C$70,1,FIND("-",[24]AP准则!$C$2:$C$70)-1))*(Q16&lt;=--MID([24]AP准则!$C$2:$C$70,FIND("-",[24]AP准则!$C$2:$C$70)+1,2))),[24]AP准则!$D$2:$D$70))</f>
-        <v/>
-      </c>
+      <c r="R16" s="100" t="n"/>
       <c r="S16" s="65" t="n"/>
       <c r="T16" s="65" t="n"/>
       <c r="U16" s="65" t="n"/>
@@ -8998,10 +8982,7 @@
       <c r="O17" s="65" t="n"/>
       <c r="P17" s="65" t="n"/>
       <c r="Q17" s="65" t="n"/>
-      <c r="R17" s="100">
-        <f>IF(OR(K17="",O17="",Q17=""),"-",LOOKUP(1,0/((K17&gt;=--MID([24]AP准则!$A$2:$A$70,1,FIND("-",[24]AP准则!$A$2:$A$70)-1))*(K17&lt;=--MID([24]AP准则!$A$2:$A$70,FIND("-",[24]AP准则!$A$2:$A$70)+1,2))*(O17&gt;=--MID([24]AP准则!$B$2:$B$70,1,FIND("-",[24]AP准则!$B$2:$B$70)-1))*(O17&lt;=--MID([24]AP准则!$B$2:$B$70,FIND("-",[24]AP准则!$B$2:$B$70)+1,2))*(Q17&gt;=--MID([24]AP准则!$C$2:$C$70,1,FIND("-",[24]AP准则!$C$2:$C$70)-1))*(Q17&lt;=--MID([24]AP准则!$C$2:$C$70,FIND("-",[24]AP准则!$C$2:$C$70)+1,2))),[24]AP准则!$D$2:$D$70))</f>
-        <v/>
-      </c>
+      <c r="R17" s="100" t="n"/>
       <c r="S17" s="65" t="n"/>
       <c r="T17" s="65" t="n"/>
       <c r="U17" s="65" t="n"/>
@@ -9035,10 +9016,7 @@
       <c r="O18" s="65" t="n"/>
       <c r="P18" s="67" t="n"/>
       <c r="Q18" s="65" t="n"/>
-      <c r="R18" s="100">
-        <f>IF(OR(K18="",O18="",Q18=""),"-",LOOKUP(1,0/((K18&gt;=--MID([24]AP准则!$A$2:$A$70,1,FIND("-",[24]AP准则!$A$2:$A$70)-1))*(K18&lt;=--MID([24]AP准则!$A$2:$A$70,FIND("-",[24]AP准则!$A$2:$A$70)+1,2))*(O18&gt;=--MID([24]AP准则!$B$2:$B$70,1,FIND("-",[24]AP准则!$B$2:$B$70)-1))*(O18&lt;=--MID([24]AP准则!$B$2:$B$70,FIND("-",[24]AP准则!$B$2:$B$70)+1,2))*(Q18&gt;=--MID([24]AP准则!$C$2:$C$70,1,FIND("-",[24]AP准则!$C$2:$C$70)-1))*(Q18&lt;=--MID([24]AP准则!$C$2:$C$70,FIND("-",[24]AP准则!$C$2:$C$70)+1,2))),[24]AP准则!$D$2:$D$70))</f>
-        <v/>
-      </c>
+      <c r="R18" s="100" t="n"/>
       <c r="S18" s="65" t="n"/>
       <c r="T18" s="65" t="n"/>
       <c r="U18" s="65" t="n"/>
@@ -10708,7 +10686,7 @@
     <row r="1" ht="20" customFormat="1" customHeight="1" s="20">
       <c r="D1" s="29" t="inlineStr">
         <is>
-          <t>过程失效模式及后果分析（PFMEA）  （标准表格）</t>
+          <t>Process FMEA (PFMEA) — Standard Form</t>
         </is>
       </c>
       <c r="E1" s="93" t="n"/>
@@ -10764,7 +10742,7 @@
     <row r="3" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Company Name:</t>
+          <t>Company name:</t>
         </is>
       </c>
       <c r="E3" s="33" t="n"/>
@@ -10772,7 +10750,7 @@
       <c r="G3" s="96" t="n"/>
       <c r="H3" s="32" t="inlineStr">
         <is>
-          <t>项目名称：</t>
+          <t>Project name:</t>
         </is>
       </c>
       <c r="I3" s="33" t="n"/>
@@ -10784,7 +10762,7 @@
       <c r="O3" s="96" t="n"/>
       <c r="P3" s="32" t="inlineStr">
         <is>
-          <t>PFMEA ID编号：</t>
+          <t>PFMEA ID:</t>
         </is>
       </c>
       <c r="Q3" s="33" t="n"/>
@@ -10809,7 +10787,7 @@
     <row r="4" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Plant Address:</t>
+          <t>Plant address:</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -10817,7 +10795,7 @@
       <c r="G4" s="96" t="n"/>
       <c r="H4" s="32" t="inlineStr">
         <is>
-          <t>PFMEA开始时间：</t>
+          <t>PFMEA start date:</t>
         </is>
       </c>
       <c r="I4" s="52" t="n"/>
@@ -10829,7 +10807,7 @@
       <c r="O4" s="96" t="n"/>
       <c r="P4" s="34" t="inlineStr">
         <is>
-          <t>过程职责：</t>
+          <t>Process responsibility:</t>
         </is>
       </c>
       <c r="Q4" s="33" t="n"/>
@@ -10854,7 +10832,7 @@
     <row r="5" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>Customer Name:</t>
+          <t>Customer name:</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -10862,7 +10840,7 @@
       <c r="G5" s="96" t="n"/>
       <c r="H5" s="32" t="inlineStr">
         <is>
-          <t>PFMEA修订时间：</t>
+          <t>PFMEA revision date:</t>
         </is>
       </c>
       <c r="I5" s="52" t="n"/>
@@ -10874,7 +10852,7 @@
       <c r="O5" s="96" t="n"/>
       <c r="P5" s="32" t="inlineStr">
         <is>
-          <t>保密等级：</t>
+          <t>Confidentiality level:</t>
         </is>
       </c>
       <c r="Q5" s="33" t="n"/>
@@ -10899,7 +10877,7 @@
     <row r="6" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="D6" s="34" t="inlineStr">
         <is>
-          <t>Model Year / Project:</t>
+          <t>Model year / project:</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -10907,7 +10885,7 @@
       <c r="G6" s="96" t="n"/>
       <c r="H6" s="32" t="inlineStr">
         <is>
-          <t>跨职能小组：</t>
+          <t>Cross-functional team:</t>
         </is>
       </c>
       <c r="I6" s="53" t="n"/>
@@ -11006,12 +10984,12 @@
     <row r="9" ht="13.5" customFormat="1" customHeight="1" s="86">
       <c r="C9" s="38" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Continuous improvement</t>
         </is>
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
-          <t>System Analysis</t>
+          <t>System analysis</t>
         </is>
       </c>
       <c r="E9" s="93" t="n"/>
@@ -11021,7 +10999,7 @@
       <c r="I9" s="94" t="n"/>
       <c r="J9" s="56" t="inlineStr">
         <is>
-          <t>失效分析及降低风险</t>
+          <t>Failure analysis &amp; risk reduction</t>
         </is>
       </c>
       <c r="K9" s="93" t="n"/>
@@ -11067,7 +11045,7 @@
       <c r="I10" s="94" t="n"/>
       <c r="J10" s="40" t="inlineStr">
         <is>
-          <t>步骤4 - Failure analysis （失效分析）</t>
+          <t>Step 4 — Failure Analysis</t>
         </is>
       </c>
       <c r="K10" s="93" t="n"/>
@@ -11075,7 +11053,7 @@
       <c r="M10" s="94" t="n"/>
       <c r="N10" s="73" t="inlineStr">
         <is>
-          <t>步骤5 - Riske analysis （风险分析）</t>
+          <t>Step 5 — Risk Analysis</t>
         </is>
       </c>
       <c r="O10" s="93" t="n"/>
@@ -11087,7 +11065,7 @@
       <c r="U10" s="94" t="n"/>
       <c r="V10" s="40" t="inlineStr">
         <is>
-          <t>步骤6 - Optimization （优化）</t>
+          <t>Step 6 — Optimization</t>
         </is>
       </c>
       <c r="W10" s="93" t="n"/>
@@ -11111,44 +11089,42 @@
       </c>
       <c r="C11" s="42" t="inlineStr">
         <is>
-          <t>History / Change Authorization
-(if applicable)</t>
+          <t>History / change authorization (if applicable)</t>
         </is>
       </c>
       <c r="D11" s="43" t="inlineStr">
         <is>
-          <t>1.过程项</t>
+          <t>1. Process item</t>
         </is>
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>2.过程步骤</t>
+          <t>2. Process step</t>
         </is>
       </c>
       <c r="F11" s="45" t="inlineStr">
         <is>
-          <t>3.过程工作要素</t>
+          <t>3. Process work element</t>
         </is>
       </c>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>1.过程项目的功能</t>
+          <t>1. Process item function</t>
         </is>
       </c>
       <c r="H11" s="44" t="inlineStr">
         <is>
-          <t>2.过程步骤的功能和产品特性
-（量值为可选项）</t>
+          <t>2. Process step function and product characteristics (value optional)</t>
         </is>
       </c>
       <c r="I11" s="58" t="inlineStr">
         <is>
-          <t>3.过程工作要素的功能和过程特性</t>
+          <t>3. Process work element function and process characteristics</t>
         </is>
       </c>
       <c r="J11" s="43" t="inlineStr">
         <is>
-          <t>1.对于上一较高级别要素和\或最终用户的失效影响( FE )</t>
+          <t>1. Failure Effect (FE) on higher-level element and/or end user</t>
         </is>
       </c>
       <c r="K11" s="59" t="inlineStr">
@@ -11158,17 +11134,17 @@
       </c>
       <c r="L11" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.过程步骤的失效模式（FM） </t>
+          <t xml:space="preserve">2. Process step failure mode (FM) </t>
         </is>
       </c>
       <c r="M11" s="45" t="inlineStr">
         <is>
-          <t>3.工作要素的失效起因（FC)</t>
+          <t>3. Work element failure cause (FC)</t>
         </is>
       </c>
       <c r="N11" s="60" t="inlineStr">
         <is>
-          <t>当前对失效起因的预防控制（PC)</t>
+          <t>Current Prevention Control (PC) for failure cause</t>
         </is>
       </c>
       <c r="O11" s="59" t="inlineStr">
@@ -11178,7 +11154,7 @@
       </c>
       <c r="P11" s="60" t="inlineStr">
         <is>
-          <t>对失效起因或失效模式的当前探测控制（DC)</t>
+          <t>Current Detection Control (DC) for cause or mode</t>
         </is>
       </c>
       <c r="Q11" s="59" t="inlineStr">
@@ -11193,38 +11169,38 @@
       </c>
       <c r="S11" s="77" t="inlineStr">
         <is>
-          <t>Special Characteristics</t>
+          <t>Special characteristics</t>
         </is>
       </c>
       <c r="T11" s="78" t="inlineStr">
         <is>
-          <t>筛选符号</t>
+          <t>Filter symbol</t>
         </is>
       </c>
       <c r="U11" s="79" t="inlineStr">
         <is>
-          <t>（可选）</t>
+          <t>(optional)</t>
         </is>
       </c>
       <c r="V11" s="60" t="inlineStr">
         <is>
-          <t>Prevention Actions</t>
+          <t>Prevention actions</t>
         </is>
       </c>
       <c r="W11" s="60" t="inlineStr">
         <is>
-          <t>Detection Actions</t>
+          <t>Detection actions</t>
         </is>
       </c>
       <c r="X11" s="80" t="inlineStr">
         <is>
-          <t>Responsible姓名</t>
+          <t>Responsible person</t>
         </is>
       </c>
       <c r="Y11" s="80" t="inlineStr">
         <is>
-          <t>目标
-Completion Date</t>
+          <t>Target
+completion date</t>
         </is>
       </c>
       <c r="Z11" s="80" t="inlineStr">
@@ -11234,12 +11210,12 @@
       </c>
       <c r="AA11" s="80" t="inlineStr">
         <is>
-          <t>措施证据</t>
+          <t>Action evidence</t>
         </is>
       </c>
       <c r="AB11" s="80" t="inlineStr">
         <is>
-          <t>Completion Date</t>
+          <t>Completion date</t>
         </is>
       </c>
       <c r="AC11" s="59" t="inlineStr">
@@ -11264,7 +11240,7 @@
       </c>
       <c r="AG11" s="77" t="inlineStr">
         <is>
-          <t>Special Characteristics</t>
+          <t>Special characteristics</t>
         </is>
       </c>
       <c r="AH11" s="88" t="n"/>
@@ -13402,21 +13378,21 @@
     <row r="1" ht="27" customHeight="1" s="103">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>DFMEA 和PFMEA 的Action Priority (AP)</t>
+          <t>DFMEA and PFMEA Action Priority (AP)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" s="103">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>措施优先级是以严重度、频度以及检测评级的综合为基础的，目的是为降低风险而对各项措施进行优先排序</t>
+          <t>Action Priority is based on severity, occurrence, and detection ratings to prioritize risk reduction actions.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" s="103">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>影响</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -13426,7 +13402,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>对失效起因发生的预测</t>
+          <t>Prediction of failure cause occurrence</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -13436,7 +13412,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>探测能力</t>
+          <t>Detection capability</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -13446,7 +13422,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>措施优先级（AP）</t>
+          <t>Action Priority (AP)</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -13458,7 +13434,7 @@
     <row r="4">
       <c r="A4" s="104" t="inlineStr">
         <is>
-          <t>对产品或工 厂的影响度 非常高</t>
+          <t>Very high impact on product or plant</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
@@ -13468,7 +13444,7 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
@@ -13478,7 +13454,7 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -13500,7 +13476,7 @@
       <c r="D5" s="105" t="n"/>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -13522,7 +13498,7 @@
       <c r="D6" s="105" t="n"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
@@ -13544,7 +13520,7 @@
       <c r="D7" s="99" t="n"/>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -13564,7 +13540,7 @@
       <c r="B8" s="105" t="n"/>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -13574,7 +13550,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -13596,7 +13572,7 @@
       <c r="D9" s="105" t="n"/>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
@@ -13618,7 +13594,7 @@
       <c r="D10" s="105" t="n"/>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -13640,7 +13616,7 @@
       <c r="D11" s="99" t="n"/>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -13660,7 +13636,7 @@
       <c r="B12" s="105" t="n"/>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -13670,7 +13646,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -13692,7 +13668,7 @@
       <c r="D13" s="105" t="n"/>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -13714,7 +13690,7 @@
       <c r="D14" s="105" t="n"/>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -13736,7 +13712,7 @@
       <c r="D15" s="99" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -13756,7 +13732,7 @@
       <c r="B16" s="105" t="n"/>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -13766,7 +13742,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -13788,7 +13764,7 @@
       <c r="D17" s="105" t="n"/>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
@@ -13810,7 +13786,7 @@
       <c r="D18" s="105" t="n"/>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
@@ -13832,7 +13808,7 @@
       <c r="D19" s="99" t="n"/>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
@@ -13852,7 +13828,7 @@
       <c r="B20" s="99" t="n"/>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>非常低</t>
+          <t>Very low</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -13862,7 +13838,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>非常高 - 非常低</t>
+          <t>Very high - very low</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -13880,7 +13856,7 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>对产品或工 厂的影响度 高</t>
+          <t>High impact on product or plant</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
@@ -13890,7 +13866,7 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
@@ -13900,7 +13876,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
@@ -13922,7 +13898,7 @@
       <c r="D22" s="105" t="n"/>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
@@ -13944,7 +13920,7 @@
       <c r="D23" s="105" t="n"/>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
@@ -13966,7 +13942,7 @@
       <c r="D24" s="99" t="n"/>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
@@ -13986,7 +13962,7 @@
       <c r="B25" s="105" t="n"/>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
@@ -13996,7 +13972,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -14018,7 +13994,7 @@
       <c r="D26" s="105" t="n"/>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
@@ -14040,7 +14016,7 @@
       <c r="D27" s="105" t="n"/>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -14062,7 +14038,7 @@
       <c r="D28" s="99" t="n"/>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
@@ -14082,7 +14058,7 @@
       <c r="B29" s="105" t="n"/>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
@@ -14092,7 +14068,7 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -14114,7 +14090,7 @@
       <c r="D30" s="105" t="n"/>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
@@ -14136,7 +14112,7 @@
       <c r="D31" s="105" t="n"/>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -14158,7 +14134,7 @@
       <c r="D32" s="99" t="n"/>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -14178,7 +14154,7 @@
       <c r="B33" s="105" t="n"/>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
@@ -14188,7 +14164,7 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -14210,7 +14186,7 @@
       <c r="D34" s="105" t="n"/>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -14232,7 +14208,7 @@
       <c r="D35" s="105" t="n"/>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -14254,7 +14230,7 @@
       <c r="D36" s="99" t="n"/>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
@@ -14274,7 +14250,7 @@
       <c r="B37" s="99" t="n"/>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>非常低</t>
+          <t>Very low</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
@@ -14284,7 +14260,7 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>非常高 - 非常低</t>
+          <t>Very high - very low</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
@@ -14302,7 +14278,7 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>对产品或工 厂的影响度 中等</t>
+          <t>Moderate impact on product or plant</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
@@ -14312,7 +14288,7 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
@@ -14322,7 +14298,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -14344,7 +14320,7 @@
       <c r="D39" s="105" t="n"/>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -14366,7 +14342,7 @@
       <c r="D40" s="105" t="n"/>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
@@ -14388,7 +14364,7 @@
       <c r="D41" s="99" t="n"/>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
@@ -14408,7 +14384,7 @@
       <c r="B42" s="105" t="n"/>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
@@ -14418,7 +14394,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -14440,7 +14416,7 @@
       <c r="D43" s="105" t="n"/>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
@@ -14462,7 +14438,7 @@
       <c r="D44" s="105" t="n"/>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
@@ -14484,7 +14460,7 @@
       <c r="D45" s="99" t="n"/>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
@@ -14504,7 +14480,7 @@
       <c r="B46" s="105" t="n"/>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -14514,7 +14490,7 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -14536,7 +14512,7 @@
       <c r="D47" s="105" t="n"/>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
@@ -14558,7 +14534,7 @@
       <c r="D48" s="105" t="n"/>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
@@ -14580,7 +14556,7 @@
       <c r="D49" s="99" t="n"/>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
@@ -14600,7 +14576,7 @@
       <c r="B50" s="105" t="n"/>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -14610,7 +14586,7 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -14632,7 +14608,7 @@
       <c r="D51" s="105" t="n"/>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
@@ -14654,7 +14630,7 @@
       <c r="D52" s="105" t="n"/>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F52" s="16" t="inlineStr">
@@ -14676,7 +14652,7 @@
       <c r="D53" s="99" t="n"/>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
@@ -14696,7 +14672,7 @@
       <c r="B54" s="99" t="n"/>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>非常低</t>
+          <t>Very low</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -14706,7 +14682,7 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>非常高 - 非常低</t>
+          <t>Very high - very low</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
@@ -14724,7 +14700,7 @@
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>对产品或工 厂的影响度 低</t>
+          <t>Low impact on product or plant</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
@@ -14734,7 +14710,7 @@
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
@@ -14744,7 +14720,7 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
@@ -14766,7 +14742,7 @@
       <c r="D56" s="105" t="n"/>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
@@ -14788,7 +14764,7 @@
       <c r="D57" s="105" t="n"/>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
@@ -14810,7 +14786,7 @@
       <c r="D58" s="99" t="n"/>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
@@ -14830,7 +14806,7 @@
       <c r="B59" s="105" t="n"/>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
@@ -14840,7 +14816,7 @@
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -14862,7 +14838,7 @@
       <c r="D60" s="105" t="n"/>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
@@ -14884,7 +14860,7 @@
       <c r="D61" s="105" t="n"/>
       <c r="E61" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F61" s="16" t="inlineStr">
@@ -14906,7 +14882,7 @@
       <c r="D62" s="99" t="n"/>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F62" s="16" t="inlineStr">
@@ -14926,7 +14902,7 @@
       <c r="B63" s="105" t="n"/>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
@@ -14936,7 +14912,7 @@
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -14958,7 +14934,7 @@
       <c r="D64" s="105" t="n"/>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
@@ -14980,7 +14956,7 @@
       <c r="D65" s="105" t="n"/>
       <c r="E65" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
@@ -15002,7 +14978,7 @@
       <c r="D66" s="99" t="n"/>
       <c r="E66" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F66" s="16" t="inlineStr">
@@ -15022,7 +14998,7 @@
       <c r="B67" s="105" t="n"/>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
@@ -15032,7 +15008,7 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>低 - 非常低</t>
+          <t>Low - very low</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -15054,7 +15030,7 @@
       <c r="D68" s="105" t="n"/>
       <c r="E68" s="16" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F68" s="16" t="inlineStr">
@@ -15076,7 +15052,7 @@
       <c r="D69" s="105" t="n"/>
       <c r="E69" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F69" s="16" t="inlineStr">
@@ -15098,7 +15074,7 @@
       <c r="D70" s="99" t="n"/>
       <c r="E70" s="16" t="inlineStr">
         <is>
-          <t>非常高</t>
+          <t>Very high</t>
         </is>
       </c>
       <c r="F70" s="16" t="inlineStr">
@@ -15118,7 +15094,7 @@
       <c r="B71" s="99" t="n"/>
       <c r="C71" s="16" t="inlineStr">
         <is>
-          <t>非常低</t>
+          <t>Very low</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -15128,7 +15104,7 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>非常高 - 非常低</t>
+          <t>Very high - very low</t>
         </is>
       </c>
       <c r="F71" s="16" t="inlineStr">
@@ -15146,7 +15122,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>没有可察觉到的影响</t>
+          <t>No discernible effect</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
@@ -15156,7 +15132,7 @@
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>非常低 - 非常高</t>
+          <t>Very low - very high</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -15166,7 +15142,7 @@
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
-          <t>非常高 - 非常低</t>
+          <t>Very high - very low</t>
         </is>
       </c>
       <c r="F72" s="16" t="inlineStr">
